--- a/diseases/d018/2026-2029.xlsx
+++ b/diseases/d018/2026-2029.xlsx
@@ -7224,13 +7224,13 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="O46" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="R46" t="n">
-        <v>0.02713157893308864</v>
+        <v>0.02906954885688069</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1985</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d018/2026-2029.xlsx
+++ b/diseases/d018/2026-2029.xlsx
@@ -7910,12 +7910,12 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -7940,12 +7940,12 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N51" t="n">
@@ -7988,40 +7988,185 @@
       </c>
       <c r="AV51" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA51" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB51" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC51" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>D018</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>Hemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>D018</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>Hemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>流行性出血热</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N52" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" t="n">
+        <v>0</v>
+      </c>
+      <c r="R52" t="n">
+        <v>0</v>
+      </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO52" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP52" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR52" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS52" t="inlineStr"/>
+      <c r="AT52" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU52" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV52" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW51" t="inlineStr">
+      <c r="AW52" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
+      <c r="AX52" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY51" t="inlineStr">
+      <c r="AY52" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
+      <c r="AZ52" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA51" t="inlineStr">
+      <c r="BA52" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB51" t="inlineStr">
+      <c r="BB52" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC51" t="inlineStr">
+      <c r="BC52" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -8143,7 +8288,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="10">
@@ -8153,7 +8298,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="11">

--- a/diseases/d018/2026-2029.xlsx
+++ b/diseases/d018/2026-2029.xlsx
@@ -7185,12 +7185,12 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -7224,13 +7224,16 @@
         </is>
       </c>
       <c r="N46" t="n">
-        <v>15</v>
+        <v>112</v>
       </c>
       <c r="O46" t="n">
-        <v>15</v>
+        <v>112</v>
+      </c>
+      <c r="Q46" t="n">
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>0.02906954885688069</v>
+        <v>0.007926879695771397</v>
       </c>
       <c r="S46" t="inlineStr">
         <is>
@@ -7263,42 +7266,42 @@
       </c>
       <c r="AV46" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB46" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC46" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -7330,12 +7333,12 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
@@ -7360,7 +7363,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -7369,13 +7372,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="O47" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>0.02906954885688069</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -7408,42 +7411,42 @@
       </c>
       <c r="AV47" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB47" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC47" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -7505,7 +7508,7 @@
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
@@ -7650,7 +7653,7 @@
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
@@ -7795,7 +7798,7 @@
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>2026-08-23</t>
+          <t>2026-08-16</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
@@ -7940,7 +7943,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-23</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -8055,12 +8058,12 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -8085,12 +8088,12 @@
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="N52" t="n">
@@ -8133,40 +8136,185 @@
       </c>
       <c r="AV52" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA52" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB52" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC52" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>D018</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Hemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>D018</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>Hemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>流行性出血热</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N53" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" t="n">
+        <v>0</v>
+      </c>
+      <c r="R53" t="n">
+        <v>0</v>
+      </c>
+      <c r="S53" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO53" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP53" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR53" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS53" t="inlineStr"/>
+      <c r="AT53" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU53" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV53" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW52" t="inlineStr">
+      <c r="AW53" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
+      <c r="AX53" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY52" t="inlineStr">
+      <c r="AY53" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
+      <c r="AZ53" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA52" t="inlineStr">
+      <c r="BA53" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB52" t="inlineStr">
+      <c r="BB53" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC52" t="inlineStr">
+      <c r="BC53" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -8288,7 +8436,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="10">
@@ -8298,7 +8446,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11">
@@ -8350,7 +8498,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1986</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d018/2026-2029.xlsx
+++ b/diseases/d018/2026-2029.xlsx
@@ -8242,13 +8242,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O53" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>0.001937969923792046</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -8498,7 +8498,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2098</v>
+        <v>2099</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d018/2026-2029.xlsx
+++ b/diseases/d018/2026-2029.xlsx
@@ -8242,13 +8242,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="R53" t="n">
-        <v>0.001937969923792046</v>
+        <v>0.003875939847584092</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -8317,6 +8317,151 @@
       <c r="BC53" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>D018</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Hemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>D018</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>Hemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>流行性出血热</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>2026-09-06</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N54" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" t="n">
+        <v>0</v>
+      </c>
+      <c r="R54" t="n">
+        <v>0</v>
+      </c>
+      <c r="S54" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO54" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP54" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR54" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS54" t="inlineStr"/>
+      <c r="AT54" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU54" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV54" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA54" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB54" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC54" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -8353,7 +8498,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-09-06</t>
         </is>
       </c>
     </row>
@@ -8436,7 +8581,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="10">
@@ -8446,7 +8591,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
     </row>
     <row r="11">
@@ -8498,7 +8643,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2099</v>
+        <v>2100</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d018/2026-2029.xlsx
+++ b/diseases/d018/2026-2029.xlsx
@@ -8242,13 +8242,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O53" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R53" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.005813909771376137</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2100</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d018/2026-2029.xlsx
+++ b/diseases/d018/2026-2029.xlsx
@@ -8242,13 +8242,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O53" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R53" t="n">
-        <v>0.005813909771376137</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -8643,7 +8643,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2101</v>
+        <v>2102</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d018/2026-2029.xlsx
+++ b/diseases/d018/2026-2029.xlsx
@@ -8242,13 +8242,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O53" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R53" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.009689849618960231</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -8460,6 +8460,151 @@
         </is>
       </c>
       <c r="BC54" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>D018</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Hemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>D018</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>Hemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>流行性出血热</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>2026-09-13</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N55" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" t="n">
+        <v>0</v>
+      </c>
+      <c r="R55" t="n">
+        <v>0</v>
+      </c>
+      <c r="S55" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO55" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP55" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR55" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS55" t="inlineStr"/>
+      <c r="AT55" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU55" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV55" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA55" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB55" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC55" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -8498,7 +8643,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-06</t>
+          <t>2026-09-13</t>
         </is>
       </c>
     </row>
@@ -8581,7 +8726,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10">
@@ -8591,7 +8736,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="11">
@@ -8643,7 +8788,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2102</v>
+        <v>2103</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d018/2026-2029.xlsx
+++ b/diseases/d018/2026-2029.xlsx
@@ -8242,13 +8242,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="O53" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="R53" t="n">
-        <v>0.009689849618960231</v>
+        <v>0.02131766916171251</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -8607,6 +8607,296 @@
       <c r="BC55" t="inlineStr">
         <is>
           <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>D018</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Hemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>D018</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>Hemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>流行性出血热</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>2026-09-20</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="N56" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" t="n">
+        <v>0</v>
+      </c>
+      <c r="R56" t="n">
+        <v>0</v>
+      </c>
+      <c r="S56" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP56" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR56" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS56" t="inlineStr"/>
+      <c r="AT56" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU56" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV56" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA56" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB56" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC56" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>D018</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Hemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>D018</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>Hemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>流行性出血热</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N57" t="n">
+        <v>1</v>
+      </c>
+      <c r="O57" t="n">
+        <v>1</v>
+      </c>
+      <c r="R57" t="n">
+        <v>0.001937969923792046</v>
+      </c>
+      <c r="S57" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr"/>
+      <c r="AT57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU57" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV57" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC57" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -8643,7 +8933,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-13</t>
+          <t>2026-10-01</t>
         </is>
       </c>
     </row>
@@ -8726,7 +9016,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="10">
@@ -8736,7 +9026,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
@@ -8788,7 +9078,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2103</v>
+        <v>2110</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d018/2026-2029.xlsx
+++ b/diseases/d018/2026-2029.xlsx
@@ -8242,13 +8242,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="O53" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="R53" t="n">
-        <v>0.02131766916171251</v>
+        <v>0.0251936090092966</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -8783,12 +8783,12 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -8813,22 +8813,22 @@
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-27</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="N57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O57" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>0.001937969923792046</v>
+        <v>0</v>
       </c>
       <c r="S57" t="inlineStr">
         <is>
@@ -8861,40 +8861,185 @@
       </c>
       <c r="AV57" t="inlineStr">
         <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA57" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB57" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC57" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>D018</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Hemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>KR</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>D018</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>Hemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>流行性出血热</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>2026-10-01</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N58" t="n">
+        <v>3</v>
+      </c>
+      <c r="O58" t="n">
+        <v>3</v>
+      </c>
+      <c r="R58" t="n">
+        <v>0.005813909771376137</v>
+      </c>
+      <c r="S58" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO58" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP58" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR58" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS58" t="inlineStr"/>
+      <c r="AT58" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU58" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV58" t="inlineStr">
+        <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="AW57" t="inlineStr">
+      <c r="AW58" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
+      <c r="AX58" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="AY57" t="inlineStr">
+      <c r="AY58" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
+      <c r="AZ58" t="inlineStr">
         <is>
           <t>kdca_open_api</t>
         </is>
       </c>
-      <c r="BA57" t="inlineStr">
+      <c r="BA58" t="inlineStr">
         <is>
           <t>Korea KDCA EID</t>
         </is>
       </c>
-      <c r="BB57" t="inlineStr">
+      <c r="BB58" t="inlineStr">
         <is>
           <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
-      <c r="BC57" t="inlineStr">
+      <c r="BC58" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
         </is>
@@ -9016,7 +9161,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="10">
@@ -9026,7 +9171,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="11">
@@ -9078,7 +9223,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2110</v>
+        <v>2114</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d018/2026-2029.xlsx
+++ b/diseases/d018/2026-2029.xlsx
@@ -8242,13 +8242,13 @@
         </is>
       </c>
       <c r="N53" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="O53" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R53" t="n">
-        <v>0.0251936090092966</v>
+        <v>0.02713157893308864</v>
       </c>
       <c r="S53" t="inlineStr">
         <is>
@@ -9223,7 +9223,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2114</v>
+        <v>2115</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d018/2026-2029.xlsx
+++ b/diseases/d018/2026-2029.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -921,6 +926,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1661,6 +1671,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1806,6 +1821,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2546,6 +2566,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2691,6 +2716,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3431,6 +3461,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3576,6 +3611,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4316,6 +4356,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4461,6 +4506,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5349,6 +5399,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO33" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5494,6 +5549,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO34" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6222,6 +6282,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO39" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -6367,6 +6432,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO40" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7240,6 +7310,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO46" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -7385,6 +7460,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO47" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8255,6 +8335,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO53" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -8967,17 +9052,22 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O58" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R58" t="n">
-        <v>0.005813909771376137</v>
+        <v>0.007751879695168184</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO58" t="inlineStr">
@@ -9223,7 +9313,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2115</v>
+        <v>2116</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d018/2026-2029.xlsx
+++ b/diseases/d018/2026-2029.xlsx
@@ -9052,13 +9052,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O58" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R58" t="n">
-        <v>0.007751879695168184</v>
+        <v>0.009689849618960231</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -9132,6 +9132,151 @@
       <c r="BC58" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>D018</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>hemorrhagic-fever</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>Hemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>D018</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>Hemorrhagic Fever</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>流行性出血热</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>2026-10-04</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="N59" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" t="n">
+        <v>0</v>
+      </c>
+      <c r="R59" t="n">
+        <v>0</v>
+      </c>
+      <c r="S59" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO59" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP59" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR59" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS59" t="inlineStr"/>
+      <c r="AT59" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU59" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV59" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA59" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB59" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC59" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -9168,7 +9313,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-04</t>
         </is>
       </c>
     </row>
@@ -9251,7 +9396,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="10">
@@ -9261,7 +9406,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11">
@@ -9313,7 +9458,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2116</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d018/2026-2029.xlsx
+++ b/diseases/d018/2026-2029.xlsx
@@ -7447,13 +7447,13 @@
         </is>
       </c>
       <c r="N47" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="O47" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="R47" t="n">
-        <v>0.02906954885688069</v>
+        <v>0.03294548870446478</v>
       </c>
       <c r="S47" t="inlineStr">
         <is>
@@ -9052,13 +9052,13 @@
         </is>
       </c>
       <c r="N58" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O58" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R58" t="n">
-        <v>0.009689849618960231</v>
+        <v>0.01356578946654432</v>
       </c>
       <c r="S58" t="inlineStr">
         <is>
@@ -9458,7 +9458,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2117</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="16">
